--- a/data/portfolio_company_taiwan.xlsx
+++ b/data/portfolio_company_taiwan.xlsx
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>保健品, 美髮, 營養補充, 新加坡, Roy Ang</t>
+          <t>保健品, 美髮, 營養補充, 新加坡, Roy Ang, withevo</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>露西德, 3D, 景深, 深度感測, 電腦視覺, Han Jin</t>
+          <t>露西德, 3D, 景深, 深度感測, 電腦視覺, Han Jin, LucidPix, Lucid VR</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>體感, 遊戲, HomeCourt, 運動, 攝影機</t>
+          <t>體感, 遊戲, HomeCourt, 運動, 攝影機, Nex Playground, Playground, 萬代南夢宮, 體感遊戲</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">

--- a/data/portfolio_company_taiwan.xlsx
+++ b/data/portfolio_company_taiwan.xlsx
@@ -2111,12 +2111,12 @@
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>裝修佬教路, 爛片, 導演, 二手電腦, 慳電</t>
+          <t>裝修佬專欄, 專欄, 教路, 爛片, 導演, 二手電腦, 慳電, 慳錢</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>裝修平台, 一站式, 裝修工程, 家居, O2O, Benny Liu</t>
+          <t>Benny Liu, renovation platform, 裝修平台, 一站式, O2O, 裝修工程, 香港裝修</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
